--- a/source.xlsx
+++ b/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\linkedin-page-rss\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7FCD9EA-025E-47D6-92D6-614FAF7D920C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56D97E57-2539-4C0A-BE79-61B806F0EF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1,100 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\linkedin-page-rss\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56D97E57-2539-4C0A-BE79-61B806F0EF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
-  <si>
-    <t>Course Title</t>
-  </si>
-  <si>
-    <t>Course Link</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>1500 Questions | AWS Certified Cloud Practitioner [NEW 2026]</t>
-  </si>
-  <si>
-    <t>1500 Questions | Associate Cloud Engineer 2026</t>
-  </si>
-  <si>
-    <t>1500 Questions | Data Practitioner Certification 2026</t>
-  </si>
-  <si>
-    <t>Professional Google Workspace Administrator Mock Exam [2026]</t>
-  </si>
-  <si>
-    <t>AWS Certified Advanced Networking Specialty Mock Exam [2026]</t>
-  </si>
-  <si>
-    <t>https://www.udemy.com/course/aws-certified-cloud-practitioner-mock-test/?referralCode=F4C43ACD2E28C6EFE28C</t>
-  </si>
-  <si>
-    <t>https://www.udemy.com/course/associate-cloud-engineer-mock-test/?referralCode=947F593FD2F4ED12958A</t>
-  </si>
-  <si>
-    <t>https://www.udemy.com/course/data-practitioner-certification-mock-test/?referralCode=2D538518C50635E8E051</t>
-  </si>
-  <si>
-    <t>https://www.udemy.com/course/professional-google-workspace-administrator-mock-test/?referralCode=998BCE267637864A0BC3</t>
-  </si>
-  <si>
-    <t>https://www.udemy.com/course/aws-certified-advanced-networking-specialty-mock-test/?referralCode=002E347D35F002565D44</t>
-  </si>
-  <si>
-    <t>Pending</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -109,56 +46,100 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -196,7 +177,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -230,7 +211,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -265,10 +245,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -441,84 +420,117 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Course Title</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Course Link</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1500 Questions | AWS Certified Cloud Practitioner [NEW 2026]</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>https://www.udemy.com/course/aws-certified-cloud-practitioner-mock-test/?referralCode=F4C43ACD2E28C6EFE28C</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1500 Questions | Associate Cloud Engineer 2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://www.udemy.com/course/associate-cloud-engineer-mock-test/?referralCode=947F593FD2F4ED12958A</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1500 Questions | Data Practitioner Certification 2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://www.udemy.com/course/data-practitioner-certification-mock-test/?referralCode=2D538518C50635E8E051</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Professional Google Workspace Administrator Mock Exam [2026]</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://www.udemy.com/course/professional-google-workspace-administrator-mock-test/?referralCode=998BCE267637864A0BC3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AWS Certified Advanced Networking Specialty Mock Exam [2026]</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://www.udemy.com/course/aws-certified-advanced-networking-specialty-mock-test/?referralCode=002E347D35F002565D44</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="B4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="B5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="B6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/source.xlsx
+++ b/source.xlsx
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1,37 +1,123 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\linkedin-page-rss\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7A4CAB-FE54-4976-82DF-B541C70C9664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+  <si>
+    <t>Course Title</t>
+  </si>
+  <si>
+    <t>Course Link</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>1500 Questions | AWS Certified Cloud Practitioner [NEW 2026]</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/aws-certified-cloud-practitioner-mock-test/?referralCode=F4C43ACD2E28C6EFE28C</t>
+  </si>
+  <si>
+    <t>done</t>
+  </si>
+  <si>
+    <t>1500 Questions | Associate Cloud Engineer 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/associate-cloud-engineer-mock-test/?referralCode=947F593FD2F4ED12958A</t>
+  </si>
+  <si>
+    <t>1500 Questions | Data Practitioner Certification 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/data-practitioner-certification-mock-test/?referralCode=2D538518C50635E8E051</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>Professional Google Workspace Administrator Mock Exam [2026]</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/professional-google-workspace-administrator-mock-test/?referralCode=998BCE267637864A0BC3</t>
+  </si>
+  <si>
+    <t>AWS Certified Advanced Networking Specialty Mock Exam [2026]</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/aws-certified-advanced-networking-specialty-mock-test/?referralCode=002E347D35F002565D44</t>
+  </si>
+  <si>
+    <t>1500 Questions | AWS Certified Data Engineer– Associate 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/aws-certified-data-engineer-associate-mock-test/?referralCode=58669B14AB64EFA87961</t>
+  </si>
+  <si>
+    <t>1500 Questions | AWS Certified AI Practitioner 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/aws-certified-ai-practitioner-mock-test/?referralCode=D47A93540057835AA494</t>
+  </si>
+  <si>
+    <t>1500 Questions | AWS CloudOps Engineer Associate 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/aws-cloudops-engineer-associate-mock-test/?referralCode=A7D87E1E28B75C63F1E3</t>
+  </si>
+  <si>
+    <t>1500 Questions | AWS Certified Developer – Associate 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/aws-certified-developer-associate-mock-test/?referralCode=6B983AB4016D715D84CB</t>
+  </si>
+  <si>
+    <t>1500 Questions | AWS Certified DevOps Pro 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/aws-certified-devops-pro-mock-test/?referralCode=3781FAE259E0E89C23A7</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +132,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,114 +456,133 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="55.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="111" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Course Title</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Course Link</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1500 Questions | AWS Certified Cloud Practitioner [NEW 2026]</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>https://www.udemy.com/course/aws-certified-cloud-practitioner-mock-test/?referralCode=F4C43ACD2E28C6EFE28C</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1500 Questions | Associate Cloud Engineer 2026</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://www.udemy.com/course/associate-cloud-engineer-mock-test/?referralCode=947F593FD2F4ED12958A</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1500 Questions | Data Practitioner Certification 2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>https://www.udemy.com/course/data-practitioner-certification-mock-test/?referralCode=2D538518C50635E8E051</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Professional Google Workspace Administrator Mock Exam [2026]</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>https://www.udemy.com/course/professional-google-workspace-administrator-mock-test/?referralCode=998BCE267637864A0BC3</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AWS Certified Advanced Networking Specialty Mock Exam [2026]</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>https://www.udemy.com/course/aws-certified-advanced-networking-specialty-mock-test/?referralCode=002E347D35F002565D44</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1,123 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\linkedin-page-rss\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7A4CAB-FE54-4976-82DF-B541C70C9664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
-  <si>
-    <t>Course Title</t>
-  </si>
-  <si>
-    <t>Course Link</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>1500 Questions | AWS Certified Cloud Practitioner [NEW 2026]</t>
-  </si>
-  <si>
-    <t>https://www.udemy.com/course/aws-certified-cloud-practitioner-mock-test/?referralCode=F4C43ACD2E28C6EFE28C</t>
-  </si>
-  <si>
-    <t>done</t>
-  </si>
-  <si>
-    <t>1500 Questions | Associate Cloud Engineer 2026</t>
-  </si>
-  <si>
-    <t>https://www.udemy.com/course/associate-cloud-engineer-mock-test/?referralCode=947F593FD2F4ED12958A</t>
-  </si>
-  <si>
-    <t>1500 Questions | Data Practitioner Certification 2026</t>
-  </si>
-  <si>
-    <t>https://www.udemy.com/course/data-practitioner-certification-mock-test/?referralCode=2D538518C50635E8E051</t>
-  </si>
-  <si>
-    <t>Pending</t>
-  </si>
-  <si>
-    <t>Professional Google Workspace Administrator Mock Exam [2026]</t>
-  </si>
-  <si>
-    <t>https://www.udemy.com/course/professional-google-workspace-administrator-mock-test/?referralCode=998BCE267637864A0BC3</t>
-  </si>
-  <si>
-    <t>AWS Certified Advanced Networking Specialty Mock Exam [2026]</t>
-  </si>
-  <si>
-    <t>https://www.udemy.com/course/aws-certified-advanced-networking-specialty-mock-test/?referralCode=002E347D35F002565D44</t>
-  </si>
-  <si>
-    <t>1500 Questions | AWS Certified Data Engineer– Associate 2026</t>
-  </si>
-  <si>
-    <t>https://www.udemy.com/course/aws-certified-data-engineer-associate-mock-test/?referralCode=58669B14AB64EFA87961</t>
-  </si>
-  <si>
-    <t>1500 Questions | AWS Certified AI Practitioner 2026</t>
-  </si>
-  <si>
-    <t>https://www.udemy.com/course/aws-certified-ai-practitioner-mock-test/?referralCode=D47A93540057835AA494</t>
-  </si>
-  <si>
-    <t>1500 Questions | AWS CloudOps Engineer Associate 2026</t>
-  </si>
-  <si>
-    <t>https://www.udemy.com/course/aws-cloudops-engineer-associate-mock-test/?referralCode=A7D87E1E28B75C63F1E3</t>
-  </si>
-  <si>
-    <t>1500 Questions | AWS Certified Developer – Associate 2026</t>
-  </si>
-  <si>
-    <t>https://www.udemy.com/course/aws-certified-developer-associate-mock-test/?referralCode=6B983AB4016D715D84CB</t>
-  </si>
-  <si>
-    <t>1500 Questions | AWS Certified DevOps Pro 2026</t>
-  </si>
-  <si>
-    <t>https://www.udemy.com/course/aws-certified-devops-pro-mock-test/?referralCode=3781FAE259E0E89C23A7</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -132,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -456,133 +420,199 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="55.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="111" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" t="s">
-        <v>10</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Course Title</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Course Link</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1500 Questions | AWS Certified Cloud Practitioner [NEW 2026]</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>https://www.udemy.com/course/aws-certified-cloud-practitioner-mock-test/?referralCode=F4C43ACD2E28C6EFE28C</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1500 Questions | Associate Cloud Engineer 2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://www.udemy.com/course/associate-cloud-engineer-mock-test/?referralCode=947F593FD2F4ED12958A</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1500 Questions | Data Practitioner Certification 2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://www.udemy.com/course/data-practitioner-certification-mock-test/?referralCode=2D538518C50635E8E051</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Professional Google Workspace Administrator Mock Exam [2026]</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://www.udemy.com/course/professional-google-workspace-administrator-mock-test/?referralCode=998BCE267637864A0BC3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AWS Certified Advanced Networking Specialty Mock Exam [2026]</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://www.udemy.com/course/aws-certified-advanced-networking-specialty-mock-test/?referralCode=002E347D35F002565D44</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1500 Questions | AWS Certified Data Engineer– Associate 2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://www.udemy.com/course/aws-certified-data-engineer-associate-mock-test/?referralCode=58669B14AB64EFA87961</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1500 Questions | AWS Certified AI Practitioner 2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://www.udemy.com/course/aws-certified-ai-practitioner-mock-test/?referralCode=D47A93540057835AA494</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1500 Questions | AWS CloudOps Engineer Associate 2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://www.udemy.com/course/aws-cloudops-engineer-associate-mock-test/?referralCode=A7D87E1E28B75C63F1E3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1500 Questions | AWS Certified Developer – Associate 2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://www.udemy.com/course/aws-certified-developer-associate-mock-test/?referralCode=6B983AB4016D715D84CB</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1500 Questions | AWS Certified DevOps Pro 2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://www.udemy.com/course/aws-certified-devops-pro-mock-test/?referralCode=3781FAE259E0E89C23A7</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1,37 +1,124 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
+  <si>
+    <t>Course Title</t>
+  </si>
+  <si>
+    <t>Course Link</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>1500 Questions | AWS Certified Cloud Practitioner [NEW 2026]</t>
+  </si>
+  <si>
+    <t>1500 Questions | Associate Cloud Engineer 2026</t>
+  </si>
+  <si>
+    <t>1500 Questions | Data Practitioner Certification 2026</t>
+  </si>
+  <si>
+    <t>Professional Google Workspace Administrator Mock Exam [2026]</t>
+  </si>
+  <si>
+    <t>AWS Certified Advanced Networking Specialty Mock Exam [2026]</t>
+  </si>
+  <si>
+    <t>1500 Questions | AWS Certified Data Engineer– Associate 2026</t>
+  </si>
+  <si>
+    <t>1500 Questions | AWS Certified AI Practitioner 2026</t>
+  </si>
+  <si>
+    <t>1500 Questions | AWS CloudOps Engineer Associate 2026</t>
+  </si>
+  <si>
+    <t>1500 Questions | AWS Certified Developer – Associate 2026</t>
+  </si>
+  <si>
+    <t>1500 Questions | AWS Certified DevOps Pro 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/aws-certified-cloud-practitioner-mock-test/?referralCode=F4C43ACD2E28C6EFE28C</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/associate-cloud-engineer-mock-test/?referralCode=947F593FD2F4ED12958A</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/data-practitioner-certification-mock-test/?referralCode=2D538518C50635E8E051</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/professional-google-workspace-administrator-mock-test/?referralCode=998BCE267637864A0BC3</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/aws-certified-advanced-networking-specialty-mock-test/?referralCode=002E347D35F002565D44</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/aws-certified-data-engineer-associate-mock-test/?referralCode=58669B14AB64EFA87961</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/aws-certified-ai-practitioner-mock-test/?referralCode=D47A93540057835AA494</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/aws-cloudops-engineer-associate-mock-test/?referralCode=A7D87E1E28B75C63F1E3</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/aws-certified-developer-associate-mock-test/?referralCode=6B983AB4016D715D84CB</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/aws-certified-devops-pro-mock-test/?referralCode=3781FAE259E0E89C23A7</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +133,41 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,202 +455,144 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Course Title</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Course Link</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1500 Questions | AWS Certified Cloud Practitioner [NEW 2026]</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>https://www.udemy.com/course/aws-certified-cloud-practitioner-mock-test/?referralCode=F4C43ACD2E28C6EFE28C</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1500 Questions | Associate Cloud Engineer 2026</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://www.udemy.com/course/associate-cloud-engineer-mock-test/?referralCode=947F593FD2F4ED12958A</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1500 Questions | Data Practitioner Certification 2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>https://www.udemy.com/course/data-practitioner-certification-mock-test/?referralCode=2D538518C50635E8E051</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Professional Google Workspace Administrator Mock Exam [2026]</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>https://www.udemy.com/course/professional-google-workspace-administrator-mock-test/?referralCode=998BCE267637864A0BC3</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AWS Certified Advanced Networking Specialty Mock Exam [2026]</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>https://www.udemy.com/course/aws-certified-advanced-networking-specialty-mock-test/?referralCode=002E347D35F002565D44</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>1500 Questions | AWS Certified Data Engineer– Associate 2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>https://www.udemy.com/course/aws-certified-data-engineer-associate-mock-test/?referralCode=58669B14AB64EFA87961</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>1500 Questions | AWS Certified AI Practitioner 2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>https://www.udemy.com/course/aws-certified-ai-practitioner-mock-test/?referralCode=D47A93540057835AA494</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>1500 Questions | AWS CloudOps Engineer Associate 2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>https://www.udemy.com/course/aws-cloudops-engineer-associate-mock-test/?referralCode=A7D87E1E28B75C63F1E3</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>1500 Questions | AWS Certified Developer – Associate 2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://www.udemy.com/course/aws-certified-developer-associate-mock-test/?referralCode=6B983AB4016D715D84CB</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>1500 Questions | AWS Certified DevOps Pro 2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>https://www.udemy.com/course/aws-certified-devops-pro-mock-test/?referralCode=3781FAE259E0E89C23A7</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1"/>
+    <hyperlink ref="B3" r:id="rId2"/>
+    <hyperlink ref="B4" r:id="rId3"/>
+    <hyperlink ref="B5" r:id="rId4"/>
+    <hyperlink ref="B6" r:id="rId5"/>
+    <hyperlink ref="B7" r:id="rId6"/>
+    <hyperlink ref="B8" r:id="rId7"/>
+    <hyperlink ref="B9" r:id="rId8"/>
+    <hyperlink ref="B10" r:id="rId9"/>
+    <hyperlink ref="B11" r:id="rId10"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/source.xlsx
+++ b/source.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <t>Course Title</t>
   </si>
@@ -83,6 +83,9 @@
   </si>
   <si>
     <t>https://www.udemy.com/course/aws-certified-devops-pro-mock-test/?referralCode=3781FAE259E0E89C23A7</t>
+  </si>
+  <si>
+    <t>done</t>
   </si>
   <si>
     <t>Pending</t>
@@ -489,7 +492,7 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -500,7 +503,7 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -511,7 +514,7 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -522,7 +525,7 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -533,7 +536,7 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -544,7 +547,7 @@
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -555,7 +558,7 @@
         <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -566,7 +569,7 @@
         <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -577,7 +580,7 @@
         <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1,127 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
-  <si>
-    <t>Course Title</t>
-  </si>
-  <si>
-    <t>Course Link</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>1500 Questions | AWS Certified Cloud Practitioner [NEW 2026]</t>
-  </si>
-  <si>
-    <t>1500 Questions | Associate Cloud Engineer 2026</t>
-  </si>
-  <si>
-    <t>1500 Questions | Data Practitioner Certification 2026</t>
-  </si>
-  <si>
-    <t>Professional Google Workspace Administrator Mock Exam [2026]</t>
-  </si>
-  <si>
-    <t>AWS Certified Advanced Networking Specialty Mock Exam [2026]</t>
-  </si>
-  <si>
-    <t>1500 Questions | AWS Certified Data Engineer– Associate 2026</t>
-  </si>
-  <si>
-    <t>1500 Questions | AWS Certified AI Practitioner 2026</t>
-  </si>
-  <si>
-    <t>1500 Questions | AWS CloudOps Engineer Associate 2026</t>
-  </si>
-  <si>
-    <t>1500 Questions | AWS Certified Developer – Associate 2026</t>
-  </si>
-  <si>
-    <t>1500 Questions | AWS Certified DevOps Pro 2026</t>
-  </si>
-  <si>
-    <t>https://www.udemy.com/course/aws-certified-cloud-practitioner-mock-test/?referralCode=F4C43ACD2E28C6EFE28C</t>
-  </si>
-  <si>
-    <t>https://www.udemy.com/course/associate-cloud-engineer-mock-test/?referralCode=947F593FD2F4ED12958A</t>
-  </si>
-  <si>
-    <t>https://www.udemy.com/course/data-practitioner-certification-mock-test/?referralCode=2D538518C50635E8E051</t>
-  </si>
-  <si>
-    <t>https://www.udemy.com/course/professional-google-workspace-administrator-mock-test/?referralCode=998BCE267637864A0BC3</t>
-  </si>
-  <si>
-    <t>https://www.udemy.com/course/aws-certified-advanced-networking-specialty-mock-test/?referralCode=002E347D35F002565D44</t>
-  </si>
-  <si>
-    <t>https://www.udemy.com/course/aws-certified-data-engineer-associate-mock-test/?referralCode=58669B14AB64EFA87961</t>
-  </si>
-  <si>
-    <t>https://www.udemy.com/course/aws-certified-ai-practitioner-mock-test/?referralCode=D47A93540057835AA494</t>
-  </si>
-  <si>
-    <t>https://www.udemy.com/course/aws-cloudops-engineer-associate-mock-test/?referralCode=A7D87E1E28B75C63F1E3</t>
-  </si>
-  <si>
-    <t>https://www.udemy.com/course/aws-certified-developer-associate-mock-test/?referralCode=6B983AB4016D715D84CB</t>
-  </si>
-  <si>
-    <t>https://www.udemy.com/course/aws-certified-devops-pro-mock-test/?referralCode=3781FAE259E0E89C23A7</t>
-  </si>
-  <si>
-    <t>done</t>
-  </si>
-  <si>
-    <t>Pending</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -136,41 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -458,144 +420,202 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" t="s">
-        <v>24</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Course Title</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Course Link</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1500 Questions | AWS Certified Cloud Practitioner [NEW 2026]</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>https://www.udemy.com/course/aws-certified-cloud-practitioner-mock-test/?referralCode=F4C43ACD2E28C6EFE28C</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1500 Questions | Associate Cloud Engineer 2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://www.udemy.com/course/associate-cloud-engineer-mock-test/?referralCode=947F593FD2F4ED12958A</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1500 Questions | Data Practitioner Certification 2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://www.udemy.com/course/data-practitioner-certification-mock-test/?referralCode=2D538518C50635E8E051</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Professional Google Workspace Administrator Mock Exam [2026]</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://www.udemy.com/course/professional-google-workspace-administrator-mock-test/?referralCode=998BCE267637864A0BC3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AWS Certified Advanced Networking Specialty Mock Exam [2026]</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://www.udemy.com/course/aws-certified-advanced-networking-specialty-mock-test/?referralCode=002E347D35F002565D44</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1500 Questions | AWS Certified Data Engineer– Associate 2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://www.udemy.com/course/aws-certified-data-engineer-associate-mock-test/?referralCode=58669B14AB64EFA87961</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1500 Questions | AWS Certified AI Practitioner 2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://www.udemy.com/course/aws-certified-ai-practitioner-mock-test/?referralCode=D47A93540057835AA494</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1500 Questions | AWS CloudOps Engineer Associate 2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://www.udemy.com/course/aws-cloudops-engineer-associate-mock-test/?referralCode=A7D87E1E28B75C63F1E3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1500 Questions | AWS Certified Developer – Associate 2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://www.udemy.com/course/aws-certified-developer-associate-mock-test/?referralCode=6B983AB4016D715D84CB</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1500 Questions | AWS Certified DevOps Pro 2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://www.udemy.com/course/aws-certified-devops-pro-mock-test/?referralCode=3781FAE259E0E89C23A7</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1"/>
-    <hyperlink ref="B3" r:id="rId2"/>
-    <hyperlink ref="B4" r:id="rId3"/>
-    <hyperlink ref="B5" r:id="rId4"/>
-    <hyperlink ref="B6" r:id="rId5"/>
-    <hyperlink ref="B7" r:id="rId6"/>
-    <hyperlink ref="B8" r:id="rId7"/>
-    <hyperlink ref="B9" r:id="rId8"/>
-    <hyperlink ref="B10" r:id="rId9"/>
-    <hyperlink ref="B11" r:id="rId10"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/source.xlsx
+++ b/source.xlsx
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -594,7 +594,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -611,7 +611,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1,37 +1,257 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\linkedin-page-rss\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF1F3846-C6A6-43A4-94B8-89BDF24F263C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="67">
+  <si>
+    <t>Course Title</t>
+  </si>
+  <si>
+    <t>Course Link</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>1500 Questions | AWS Certified Cloud Practitioner [NEW 2026]</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/aws-certified-cloud-practitioner-mock-test/?referralCode=F4C43ACD2E28C6EFE28C</t>
+  </si>
+  <si>
+    <t>done</t>
+  </si>
+  <si>
+    <t>1500 Questions | Associate Cloud Engineer 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/associate-cloud-engineer-mock-test/?referralCode=947F593FD2F4ED12958A</t>
+  </si>
+  <si>
+    <t>1500 Questions | Data Practitioner Certification 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/data-practitioner-certification-mock-test/?referralCode=2D538518C50635E8E051</t>
+  </si>
+  <si>
+    <t>Professional Google Workspace Administrator Mock Exam [2026]</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/professional-google-workspace-administrator-mock-test/?referralCode=998BCE267637864A0BC3</t>
+  </si>
+  <si>
+    <t>AWS Certified Advanced Networking Specialty Mock Exam [2026]</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/aws-certified-advanced-networking-specialty-mock-test/?referralCode=002E347D35F002565D44</t>
+  </si>
+  <si>
+    <t>1500 Questions | AWS Certified Data Engineer– Associate 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/aws-certified-data-engineer-associate-mock-test/?referralCode=58669B14AB64EFA87961</t>
+  </si>
+  <si>
+    <t>1500 Questions | AWS Certified AI Practitioner 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/aws-certified-ai-practitioner-mock-test/?referralCode=D47A93540057835AA494</t>
+  </si>
+  <si>
+    <t>1500 Questions | AWS CloudOps Engineer Associate 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/aws-cloudops-engineer-associate-mock-test/?referralCode=A7D87E1E28B75C63F1E3</t>
+  </si>
+  <si>
+    <t>1500 Questions | AWS Certified Developer – Associate 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/aws-certified-developer-associate-mock-test/?referralCode=6B983AB4016D715D84CB</t>
+  </si>
+  <si>
+    <t>1500 Questions | AWS Certified DevOps Pro 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/aws-certified-devops-pro-mock-test/?referralCode=3781FAE259E0E89C23A7</t>
+  </si>
+  <si>
+    <t>1500 Questions | AWS Machine Learning Specialty 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/aws-machine-learning-specialty-mock-test/?referralCode=2D33C0BC430140B77BF0</t>
+  </si>
+  <si>
+    <t>1500 Questions | AWS ML Engineer Associate (MLA-C01) 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/aws-ml-engineer-associate-mla-c01-mock-test/?referralCode=D3EDF5AD569B35A430AB</t>
+  </si>
+  <si>
+    <t>1500 Questions | AWS Certified Security – Specialty 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/aws-certified-security-specialty-mock-test/?referralCode=CDEDCB759B77D776800F</t>
+  </si>
+  <si>
+    <t>1500 Questions | AWS Solutions Architect – Associate 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/aws-solutions-architect-associate-mock-test/?referralCode=0A6FC92C5F39EAEEC86B</t>
+  </si>
+  <si>
+    <t>1500 Questions | AWS SA Pro: SAP-C02 Masterclass 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/aws-sa-pro-sap-c02-masterclass-mock-test/?referralCode=A51B2D96C5AD567942CC</t>
+  </si>
+  <si>
+    <t>1500 Questions | Windows Server Hybrid Core: AZ-800 Guide</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/windows-server-hybrid-core-az-800-guide-mock-test/?referralCode=3AE4B90C0935CB19E531</t>
+  </si>
+  <si>
+    <t>1500 Questions | Blue Prism Certified Developer 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/blue-prism-certified-developer-mock-test/?referralCode=6F32194231D09DFCDD14</t>
+  </si>
+  <si>
+    <t>Certificate of Cloud Security Knowledge V.4 Mock Exam Test</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/certificate-of-cloud-security-knowledge-v4-mock-test/?referralCode=A8ADED9BD083F56A4563</t>
+  </si>
+  <si>
+    <t>1500 Questions | Certified Application Developer 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/certified-application-developer-mock-test/?referralCode=018A744CEA79F7038B46</t>
+  </si>
+  <si>
+    <t>1500 Questions | Certified in Cybersecurity (CC) 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/certified-in-cybersecurity-cc-mock-test/?referralCode=5279B44EC18216A92371</t>
+  </si>
+  <si>
+    <t>1500 Questions | CRISC™ Exam Preparation 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/crisctm-exam-preparation-mock-test/?referralCode=B47CDF500ADB52FEFA72</t>
+  </si>
+  <si>
+    <t>1500 Questions | CISSP Certification Guide 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/cissp-certification-guide-mock-test/?referralCode=AA0D550661B28CD79334</t>
+  </si>
+  <si>
+    <t>1500 Questions | CompTIA CySA+ Certification 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/comptia-cysa-certification-mock-test/?referralCode=DEB847437A0C4CF3BFBE</t>
+  </si>
+  <si>
+    <t>1500 Questions | CompTIA Data+ Certification 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/comptia-data-certification-mock-test/?referralCode=0B5A5A021EFF31651840</t>
+  </si>
+  <si>
+    <t>1500 Questions | CompTIA DataSys+ Certification 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/comptia-datasys-certification-mock-test/?referralCode=6794A7DE65E753ABDCB4</t>
+  </si>
+  <si>
+    <t>1500 Questions | CompTIA Linux+ Certification 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/comptia-linux-certification-mock-test/?referralCode=6536592A0A7B5B1CDED7</t>
+  </si>
+  <si>
+    <t>1500 Questions | CompTIA PenTest+ Certification 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/comptia-pentest-certification-mock-test/?referralCode=100D5AB58DB2DAF94AF7</t>
+  </si>
+  <si>
+    <t>1500 Questions | CompTIA Project+ Certification 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/comptia-project-certification-mock-test/?referralCode=DE441609ED5DF19C232B</t>
+  </si>
+  <si>
+    <t>1500 Questions | CompTIA Security+ Certification 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/comptia-security-certification-mock-test/?referralCode=F3CF5003EF061D71CD15</t>
+  </si>
+  <si>
+    <t>1500 Questions | CompTIA SecurityX Certification 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/comptia-securityx-certification-mock-test/?referralCode=512EB14C2BEA1B830E36</t>
+  </si>
+  <si>
+    <t>1500 Questions | CCSP Certification Guide 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/ccsp-certification-guide-mock-test/?referralCode=2C21637354387B7906CA</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +266,46 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,202 +593,374 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C32"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="55.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="111" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Course Title</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Course Link</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1500 Questions | AWS Certified Cloud Practitioner [NEW 2026]</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>https://www.udemy.com/course/aws-certified-cloud-practitioner-mock-test/?referralCode=F4C43ACD2E28C6EFE28C</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1500 Questions | Associate Cloud Engineer 2026</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://www.udemy.com/course/associate-cloud-engineer-mock-test/?referralCode=947F593FD2F4ED12958A</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1500 Questions | Data Practitioner Certification 2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>https://www.udemy.com/course/data-practitioner-certification-mock-test/?referralCode=2D538518C50635E8E051</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Professional Google Workspace Administrator Mock Exam [2026]</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>https://www.udemy.com/course/professional-google-workspace-administrator-mock-test/?referralCode=998BCE267637864A0BC3</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AWS Certified Advanced Networking Specialty Mock Exam [2026]</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>https://www.udemy.com/course/aws-certified-advanced-networking-specialty-mock-test/?referralCode=002E347D35F002565D44</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>1500 Questions | AWS Certified Data Engineer– Associate 2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>https://www.udemy.com/course/aws-certified-data-engineer-associate-mock-test/?referralCode=58669B14AB64EFA87961</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>1500 Questions | AWS Certified AI Practitioner 2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>https://www.udemy.com/course/aws-certified-ai-practitioner-mock-test/?referralCode=D47A93540057835AA494</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>1500 Questions | AWS CloudOps Engineer Associate 2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>https://www.udemy.com/course/aws-cloudops-engineer-associate-mock-test/?referralCode=A7D87E1E28B75C63F1E3</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>1500 Questions | AWS Certified Developer – Associate 2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://www.udemy.com/course/aws-certified-developer-associate-mock-test/?referralCode=6B983AB4016D715D84CB</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>1500 Questions | AWS Certified DevOps Pro 2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>https://www.udemy.com/course/aws-certified-devops-pro-mock-test/?referralCode=3781FAE259E0E89C23A7</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>64</v>
+      </c>
+      <c r="B32" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B15" r:id="rId1" xr:uid="{97F7C9E9-5640-4117-81B9-CDF1CA771EC7}"/>
+    <hyperlink ref="B16" r:id="rId2" xr:uid="{CBC5DC56-B891-4341-80CA-33D08E0178E7}"/>
+    <hyperlink ref="B17" r:id="rId3" xr:uid="{674E16C7-5FC0-4555-B366-08CFF5138D5A}"/>
+    <hyperlink ref="B18" r:id="rId4" xr:uid="{CA9B9974-3D50-47B8-AC0F-08F42BE39158}"/>
+    <hyperlink ref="B19" r:id="rId5" xr:uid="{FD3EF95B-38C4-43C8-A123-715C153DAB52}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/source.xlsx
+++ b/source.xlsx
@@ -662,7 +662,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -696,7 +696,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -713,7 +713,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -730,7 +730,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -747,7 +747,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -764,7 +764,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -798,7 +798,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -815,7 +815,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -832,7 +832,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -866,7 +866,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -883,7 +883,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -900,7 +900,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -934,7 +934,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -951,7 +951,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -985,7 +985,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1002,7 +1002,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1053,7 +1053,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1070,7 +1070,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1087,7 +1087,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1104,7 +1104,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1121,7 +1121,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1138,7 +1138,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1172,7 +1172,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1206,7 +1206,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1240,7 +1240,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1257,7 +1257,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1274,7 +1274,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\linkedin-page-rss\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D07457F-FAB3-4910-B234-798C6DDAB7BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE63070-E3B6-431D-A48F-F686DB449723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="187">
   <si>
     <t>Course Title</t>
   </si>
@@ -539,13 +539,55 @@
   </si>
   <si>
     <t>https://www.udemy.com/course/spring-certified-professional-2024-v2-mock-test/?referralCode=66439E98B1CDB91C9843</t>
+  </si>
+  <si>
+    <t>1500 Questions | MS Dynamics 365 Field Service (MB-240)</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/ms-dynamics-365-field-service-mb-mock-test/?referralCode=773C7EE25CA0C44BC13B</t>
+  </si>
+  <si>
+    <t>1500 Questions | VCP-NV: Network Virtualization Bootcamp</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/vcp-nv-network-virtualization-bootcamp-mock-test/?referralCode=A0F11E0F6474BA8991EE</t>
+  </si>
+  <si>
+    <t>1500 Questions | VMware VCP-DCV: Master vSphere 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/vmware-vcp-dcv-master-vsphere-mock-test/?referralCode=0D529B877B256A056B11</t>
+  </si>
+  <si>
+    <t>1500 Questions | Windows Server Hybrid Admin Associate 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/windows-server-hybrid-admin-associate-mock-test/?referralCode=DBF18E93E1F67484E7BA</t>
+  </si>
+  <si>
+    <t>1500 Questions | Microsoft SC-900: Security &amp; Compliance</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/microsoft-sc-900-security-compliance-mock-test/?referralCode=09AF9028313704BA9620</t>
+  </si>
+  <si>
+    <t>1500 Questions | MCE Microsoft Certified Educator 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/mce-microsoft-certified-educator-mock-test/?referralCode=92E6A726DF55B4D0C92E</t>
+  </si>
+  <si>
+    <t>1500 Questions | Dynamics 365 F&amp;O Developer (MB-500) 2026</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/dynamics-365-fo-developer-mb-500-mock-test/?referralCode=E1E660794BA2882E0E07</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -557,6 +599,14 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -591,16 +641,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -901,7 +954,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C85"/>
+  <dimension ref="A1:C92"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="55.21875" bestFit="1" customWidth="1"/>
@@ -1842,7 +1895,87 @@
         <v>102</v>
       </c>
     </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>173</v>
+      </c>
+      <c r="B86" t="s">
+        <v>174</v>
+      </c>
+      <c r="C86" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>175</v>
+      </c>
+      <c r="B87" t="s">
+        <v>176</v>
+      </c>
+      <c r="C87" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>177</v>
+      </c>
+      <c r="B88" t="s">
+        <v>178</v>
+      </c>
+      <c r="C88" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>179</v>
+      </c>
+      <c r="B89" t="s">
+        <v>180</v>
+      </c>
+      <c r="C89" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>181</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C90" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>183</v>
+      </c>
+      <c r="B91" t="s">
+        <v>184</v>
+      </c>
+      <c r="C91" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>185</v>
+      </c>
+      <c r="B92" t="s">
+        <v>186</v>
+      </c>
+      <c r="C92" t="s">
+        <v>102</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B90" r:id="rId1" xr:uid="{D22E00F9-013E-42EB-BE3C-22E2F66C27A2}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/source.xlsx
+++ b/source.xlsx
@@ -1291,7 +1291,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1308,7 +1308,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1342,7 +1342,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1376,7 +1376,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1393,7 +1393,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1444,7 +1444,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1461,7 +1461,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1512,7 +1512,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1546,7 +1546,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1580,7 +1580,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1597,7 +1597,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1614,7 +1614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1631,7 +1631,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1648,7 +1648,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1682,7 +1682,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1699,7 +1699,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1716,7 +1716,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1733,7 +1733,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1750,7 +1750,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1767,7 +1767,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1784,7 +1784,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1801,7 +1801,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1818,7 +1818,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1835,7 +1835,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1852,7 +1852,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1869,7 +1869,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1886,7 +1886,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1903,7 +1903,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1920,7 +1920,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1937,7 +1937,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1954,7 +1954,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1971,7 +1971,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -1988,7 +1988,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -2005,7 +2005,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -2022,7 +2022,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -2039,7 +2039,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -2056,7 +2056,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -2073,7 +2073,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -2107,7 +2107,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -2124,7 +2124,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -2141,7 +2141,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -2175,7 +2175,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -2192,7 +2192,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -2209,7 +2209,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -2226,7 +2226,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -2243,7 +2243,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -2260,7 +2260,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -2277,7 +2277,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -2294,7 +2294,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -2311,7 +2311,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/source.xlsx
+++ b/source.xlsx
@@ -2328,7 +2328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>done</t>
         </is>
       </c>
     </row>
